--- a/experiment_output/TwoCombinedGames/ElapsedTimePerFilesSetsOfSevenBothCombinedGamesFinal.xlsx
+++ b/experiment_output/TwoCombinedGames/ElapsedTimePerFilesSetsOfSevenBothCombinedGamesFinal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\90948045\OneDrive - Western Sydney University\Eclipse Workspace\bandit_rule_game_theory_experiment_two_combined_games\experiment_output\TwoCombinedGames\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90948045_westernsydney_edu_au/Documents/Documents/Thesis/TwoCombinedGames/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301E9C99-54AA-4EA0-B2D0-A8E211053ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{D4395DC1-0AE3-481C-A6AA-533736355E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C12F24-A1A9-476C-9318-5B3B9C0A4B50}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" xr2:uid="{27182AD4-836B-4194-8287-A2C4FC030FAD}"/>
   </bookViews>
@@ -4890,6 +4890,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5210,9 +5214,11 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5338,10 +5344,14 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
